--- a/output/pdf_financials_xlsx/TUD.xlsx
+++ b/output/pdf_financials_xlsx/TUD.xlsx
@@ -4649,31 +4649,31 @@
         <v>0</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>-0.006712</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>-0.014076</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>0.008215</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>0.006573</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0</v>
+        <v>-0.116219</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>0</v>
+        <v>-0.024559</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>0</v>
+        <v>-0.000372</v>
       </c>
       <c r="K103" s="3" t="n">
-        <v>0</v>
+        <v>-0.063945</v>
       </c>
       <c r="L103" s="3" t="n">
-        <v>0</v>
+        <v>0.009218</v>
       </c>
     </row>
     <row r="104">
@@ -4769,31 +4769,31 @@
         <v>0.074984</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.095528</v>
+        <v>-0.10224</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.032508</v>
+        <v>-0.046584</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-0.359916</v>
+        <v>-0.351701</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.600149</v>
+        <v>0.606722</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>-0.890588</v>
+        <v>-1.006807</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>1.303316</v>
+        <v>1.278757</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>-0.043695</v>
+        <v>-0.044067</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>-0.203961</v>
+        <v>-0.267906</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0.00311</v>
+        <v>0.012328</v>
       </c>
     </row>
     <row r="107">
@@ -6391,7 +6391,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>
@@ -12236,7 +12240,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TUD.xlsx
+++ b/output/pdf_financials_xlsx/TUD.xlsx
@@ -871,7 +871,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001967</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -880,7 +880,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.013406</v>
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.08244600000000001</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.032437</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.218617</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.06443400000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1539,7 +1539,7 @@
         <v>-0.112833</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.382001</v>
+        <v>-1.383968</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-3.689268</v>
@@ -1548,7 +1548,7 @@
         <v>-3.498015</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-3.371624</v>
+        <v>-3.38503</v>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
@@ -1556,16 +1556,16 @@
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-9.805104</v>
+        <v>-9.887549999999999</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.054384</v>
+        <v>0.021947</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-3.595292</v>
+        <v>-3.813909</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-6.325398</v>
+        <v>-6.389832</v>
       </c>
     </row>
     <row r="28">
@@ -1623,7 +1623,7 @@
         <v>-0.112833</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.376839</v>
+        <v>-1.378806</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-3.666767</v>
@@ -1632,7 +1632,7 @@
         <v>-3.45775</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-3.321204</v>
+        <v>-3.33461</v>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-9.559184999999999</v>
+        <v>-9.641631</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.395798</v>
+        <v>0.363361</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-3.173667</v>
+        <v>-3.392284</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-6.07552</v>
+        <v>-6.139954</v>
       </c>
     </row>
     <row r="30">
@@ -1832,22 +1832,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.03506</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.007996</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.094303</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.302362</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.265712</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>6.087954</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>1.498669</v>
@@ -1912,22 +1912,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.03506</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.007996</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.094303</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.302362</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.265712</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>6.087954</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>1.498669</v>
@@ -2395,19 +2395,19 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.007996</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.288515</v>
+        <v>0.194212</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.4794</v>
+        <v>0.177038</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.403285</v>
+        <v>0.137573</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>6.292079</v>
+        <v>0.204125</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>1.115468</v>
@@ -5500,28 +5500,28 @@
         <v>0</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.026158</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.020607</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.020609</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.020609</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.003435</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.05808</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.05808</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.05984</v>
       </c>
     </row>
     <row r="125">
@@ -5540,28 +5540,28 @@
         <v>0</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.026158</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.020607</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.020609</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.020609</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.003435</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.05808</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.05808</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.05984</v>
       </c>
     </row>
     <row r="126">
@@ -6639,7 +6639,11 @@
           <t>Reclamation deposits (Note 4)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -8045,7 +8049,11 @@
           <t>Reclamation deposits (Note 5)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -9604,7 +9612,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
@@ -12872,7 +12880,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -13337,7 +13349,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -14971,7 +14987,11 @@
           <t>Finance lease payments</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -16625,7 +16645,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -18406,7 +18430,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -18481,7 +18505,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -21474,7 +21498,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -21545,7 +21569,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -25507,7 +25531,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">

--- a/output/pdf_financials_xlsx/TUD.xlsx
+++ b/output/pdf_financials_xlsx/TUD.xlsx
@@ -5015,7 +5015,7 @@
         <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.0075</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -15777,7 +15777,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -15996,7 +16000,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -16718,7 +16726,11 @@
           <t>Proceeds from disposition of property and equipment</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
